--- a/Essential_Links_For_Statistical_Programmers.xlsx
+++ b/Essential_Links_For_Statistical_Programmers.xlsx
@@ -43,13 +43,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Papers Conferences &amp; Learning'!$A$1:$E$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Therapeutic Area User Guides'!$A$1:$E$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Statistical Methods &amp; Guidance'!$A$1:$E$99</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'eCTD &amp; Submission Packaging'!$A$1:$E$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Pharmacovigilance &amp; Safety'!$A$1:$E$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'eCTD &amp; Submission Packaging'!$A$1:$E$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Pharmacovigilance &amp; Safety'!$A$1:$E$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Real-World Data &amp; Digital Healt'!$A$1:$E$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Biostatistics Software &amp; Valida'!$A$1:$E$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'PK_PD &amp; Pharmacometrics'!$A$1:$E$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Data Privacy &amp; Anonymization'!$A$1:$E$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Clinical Operations &amp; Project M'!$A$1:$E$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Clinical Operations &amp; Project M'!$A$1:$E$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -769,7 +769,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Curated by Mohan Peddineni  |  Principal Statistical Programmer  |  Version 6.0  |  April 2026</t>
+          <t>Curated by Mohan Peddineni  |  Principal Statistical Programmer  |  Version 7.0  |  April 2026</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2422 curated resources across 20 sections.</t>
+          <t>2419 curated resources across 20 sections.</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2422</v>
+        <v>2419</v>
       </c>
     </row>
   </sheetData>
@@ -1083,15 +1083,19 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Box-and-whisker plots for lab/vital signs by visit and treatment.</t>
+          <t>Box-and-whisker plots for lab/vital signs by visit and treatment. NEST TLG Catalog template with R code.</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/tables/lab-results/lbt05.html</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>https://r-graph-gallery.com/boxplot.html</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
@@ -1104,15 +1108,19 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Back-to-back bar chart comparing AE rates between treatments.</t>
+          <t>Back-to-back bar chart comparing AE rates between treatments. NEST catalog AE graph template.</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/adverse-events/aeg01.html</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -1125,15 +1133,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Cumulative incidence of events over time.</t>
+          <t>Cumulative incidence of events over time. NEST KM/cumulative event template.</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/efficacy/kmg01.html</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>https://cran.r-project.org/web/packages/survival/vignettes/timedep.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -1146,15 +1158,19 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Dot plots showing AE incidence by SOC/PT.</t>
+          <t>Dot/lollipop plots showing AE incidence by SOC/PT. NEST AE dot plot template.</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/adverse-events/aeg03.html</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -1167,15 +1183,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>E-R relationship visualization for PK/PD.</t>
+          <t>E-R relationship visualization for PK/PD. FDA E-R guidance + ggPMX R package for pharmacometrics plots.</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr"/>
+          <t>https://www.fda.gov/regulatory-information/search-fda-guidance-documents/exposure-response-relationships-study-design-data-analysis-and-regulatory-applications</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>https://cran.r-project.org/web/packages/ggPMX/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -1188,15 +1208,19 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Treatment effect forest plots for subgroup analyses.</t>
+          <t>Treatment effect forest plots for subgroup analyses. NEST forest plot template + forestplot R package vignette.</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/forestplot/</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/efficacy/fstg01.html</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>https://cran.r-project.org/web/packages/forestplot/vignettes/forestplot.html</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -1209,15 +1233,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Heat map visualization for lab abnormalities or AE patterns.</t>
+          <t>Heat map visualization for lab abnormalities or AE patterns. NEST individual patient plot + R Graph Gallery tutorial.</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/other/ippg01.html</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -1230,17 +1258,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Survival curve plotting in R (survminer) and SAS (PROC LIFETEST).</t>
+          <t>Survival curve plotting. NEST KM template with R code + survminer package documentation.</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/survminer/</t>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/efficacy/kmg01.html</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/statug/statug_lifetest_syntax.htm</t>
+          <t>https://rpkgs.datanovia.com/survminer/</t>
         </is>
       </c>
     </row>
@@ -1255,15 +1283,19 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Line plot with error bars for efficacy endpoints over time.</t>
+          <t>Line plot with error bars for efficacy endpoints over time. NEST mean plot template with R code.</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/efficacy/mng01.html</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -1276,15 +1308,19 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Individual patient profiles with AE/conmed/lab timelines.</t>
+          <t>Individual patient profiles with AE/conmed/lab timelines. NEST patient plot + patientProfilesVis R package.</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/other/ippg01.html</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -1297,15 +1333,19 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Visual shift analysis: baseline vs post-baseline categories.</t>
+          <t>Visual shift analysis: baseline vs post-baseline categories. NEST shift table + PhUSE shift tables white paper.</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/tables/lab-results/lbt14.html</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>https://advance.hub.phuse.global/wiki/spaces/WEL/pages/26804480/CSS+Working+Group+Deliverables</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -1318,15 +1358,19 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Individual patient trajectories over time.</t>
+          <t>Individual patient trajectories over time. NEST individual patient plot + R Graph Gallery spaghetti tutorial.</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/other/ippg01.html</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
@@ -1339,15 +1383,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Individual patient tumor size over time (spaghetti plots).</t>
+          <t>Individual patient tumor size over time (oncology spider/spaghetti). NEST spider plot template.</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/efficacy/spiderg01.html</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -1360,15 +1408,19 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Forest plot with interaction p-values for subgroup analyses.</t>
+          <t>Forest plot with interaction p-values for subgroup analyses. NEST subgroup forest template.</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/forestplot/</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/efficacy/fstg02.html</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
@@ -1381,15 +1433,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Patient-level timeline swimmer plots (oncology).</t>
+          <t>Patient-level timeline swimmer plots (oncology). NEST swimmer plot template + swimplot vignette.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/swimplot/</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/efficacy/swimlg01.html</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -1402,15 +1458,19 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Sensitivity/tornado plots for key parameter impact.</t>
+          <t>Sensitivity/tornado plots for key parameter impact. R Graph Gallery tornado chart tutorial.</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr"/>
+          <t>https://r-graph-gallery.com/web-tornado-chart-with-ggplot2.html</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -1423,15 +1483,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Response waterfall plots (oncology: tumor change from baseline).</t>
+          <t>Response waterfall plots (oncology: best % change from baseline). NEST waterfall template.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr"/>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/graphs/efficacy/waterfallg01.html</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
@@ -1444,15 +1508,19 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Evaluation of Drug-Induced Serious Hepatotoxicity plot.</t>
+          <t>Evaluation of Drug-Induced Serious Hepatotoxicity plot. FDA eDISH tool and guidance.</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>https://cran.r-project.org/web/packages/ggplot2/</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr"/>
+          <t>https://www.fda.gov/science-research/bioinformatics-tools/evaluation-drug-induced-serious-hepatotoxicity-edish</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>https://insightsengineering.github.io/tlg-catalog/stable/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -2111,60 +2179,77 @@
   <autoFilter ref="A1:E51"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2420,10 +2505,14 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
+          <t>https://www.fharrell.com/</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
           <t>https://www.biostatisticsdecoded.com/</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -6268,7 +6357,11 @@
           <t>https://www.youtube.com/@AndrewHeiss</t>
         </is>
       </c>
-      <c r="E199" s="8" t="inlineStr"/>
+      <c r="E199" s="9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Andrew+Heiss+YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="8" t="n">
@@ -6289,7 +6382,11 @@
           <t>https://www.youtube.com/@SpartacanUsuals</t>
         </is>
       </c>
-      <c r="E200" s="8" t="inlineStr"/>
+      <c r="E200" s="9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Ben+Lambert+Bayesian+YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="8" t="n">
@@ -6352,7 +6449,11 @@
           <t>https://www.youtube.com/@CytelInc</t>
         </is>
       </c>
-      <c r="E203" s="8" t="inlineStr"/>
+      <c r="E203" s="9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Cytel+clinical+trial+YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="8" t="n">
@@ -6373,7 +6474,11 @@
           <t>https://www.youtube.com/@DIAGlobal</t>
         </is>
       </c>
-      <c r="E204" s="8" t="inlineStr"/>
+      <c r="E204" s="9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=DIA+Global+YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="8" t="n">
@@ -6394,7 +6499,11 @@
           <t>https://www.youtube.com/@dataschool</t>
         </is>
       </c>
-      <c r="E205" s="8" t="inlineStr"/>
+      <c r="E205" s="9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Data+School+Kevin+Markham+YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="8" t="n">
@@ -6415,7 +6524,11 @@
           <t>https://www.youtube.com/@safe4democracy</t>
         </is>
       </c>
-      <c r="E206" s="8" t="inlineStr"/>
+      <c r="E206" s="9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=David+Robinson+TidyTuesday+YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="8" t="n">
@@ -6436,7 +6549,11 @@
           <t>https://www.youtube.com/@ICONplc</t>
         </is>
       </c>
-      <c r="E207" s="8" t="inlineStr"/>
+      <c r="E207" s="9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=ICON+plc+YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="8" t="n">
@@ -6478,7 +6595,11 @@
           <t>https://www.youtube.com/@maraboroshi</t>
         </is>
       </c>
-      <c r="E209" s="8" t="inlineStr"/>
+      <c r="E209" s="9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=MarinStatsLectures+YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="8" t="n">
@@ -6520,7 +6641,11 @@
           <t>https://www.youtube.com/@zabormetrics</t>
         </is>
       </c>
-      <c r="E211" s="8" t="inlineStr"/>
+      <c r="E211" s="9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Zedstatistics+YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="8" t="n">
@@ -6699,7 +6824,11 @@
           <t>https://www.youtube.com/@PhUSE_Global</t>
         </is>
       </c>
-      <c r="E220" s="8" t="inlineStr"/>
+      <c r="E220" s="9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=PhUSE+YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="8" t="n">
@@ -6720,7 +6849,11 @@
           <t>https://www.youtube.com/@RinPharma</t>
         </is>
       </c>
-      <c r="E221" s="8" t="inlineStr"/>
+      <c r="E221" s="9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=R+Pharma+conference+YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="8" t="n">
@@ -6833,7 +6966,11 @@
           <t>https://www.youtube.com/@useRConference</t>
         </is>
       </c>
-      <c r="E226" s="8" t="inlineStr"/>
+      <c r="E226" s="9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=useR+conference+YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="n"/>
@@ -7072,10 +7209,14 @@
       </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
+          <t>https://phrp.nihtraining.com/</t>
+        </is>
+      </c>
+      <c r="E238" s="9" t="inlineStr">
+        <is>
           <t>https://phrptraining.com/</t>
         </is>
       </c>
-      <c r="E238" s="8" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="8" t="n">
@@ -7525,10 +7666,14 @@
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
+          <t>https://seeing-theory.brown.edu/</t>
+        </is>
+      </c>
+      <c r="E261" s="9" t="inlineStr">
+        <is>
           <t>https://distribution-explorer.github.io/</t>
         </is>
       </c>
-      <c r="E261" s="8" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="8" t="n">
@@ -7609,10 +7754,14 @@
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
+          <t>https://clincalc.com/stats/samplesize.aspx</t>
+        </is>
+      </c>
+      <c r="E265" s="9" t="inlineStr">
+        <is>
           <t>https://osse.bii.a-star.edu.sg/</t>
         </is>
       </c>
-      <c r="E265" s="8" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="8" t="n">
@@ -8009,10 +8158,14 @@
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
+          <t>https://podcasts.apple.com/us/podcast/casual-inference/id1467819668</t>
+        </is>
+      </c>
+      <c r="E285" s="9" t="inlineStr">
+        <is>
           <t>https://casualinfer.libsyn.com/</t>
         </is>
       </c>
-      <c r="E285" s="8" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="8" t="n">
@@ -8030,10 +8183,14 @@
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
+          <t>https://podcasts.apple.com/</t>
+        </is>
+      </c>
+      <c r="E286" s="9" t="inlineStr">
+        <is>
           <t>https://www.clinicalresearchdecoded.com/</t>
         </is>
       </c>
-      <c r="E286" s="8" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="8" t="n">
@@ -8093,10 +8250,14 @@
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
+          <t>https://podcasts.apple.com/us/podcast/linear-digressions/id941219323</t>
+        </is>
+      </c>
+      <c r="E289" s="9" t="inlineStr">
+        <is>
           <t>https://lineardigressions.com/</t>
         </is>
       </c>
-      <c r="E289" s="8" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="8" t="n">
@@ -9882,10 +10043,14 @@
       </c>
       <c r="D376" s="9" t="inlineStr">
         <is>
+          <t>https://communities.sas.com/</t>
+        </is>
+      </c>
+      <c r="E376" s="9" t="inlineStr">
+        <is>
           <t>https://www.sasinterview.com/</t>
         </is>
       </c>
-      <c r="E376" s="8" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="8" t="n">
@@ -10603,389 +10768,409 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E371" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D398" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E371" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E376" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D398" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId412"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16163,10 +16348,14 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
+          <t>https://www.ich.org/page/ich-guidelines</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
           <t>https://database.ich.org/sites/default/files/E9-R1_Step4_Guideline_2019_1203.pdf</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -16765,15 +16954,19 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Exact test for categorical data in small sample clinical trials.</t>
+          <t>NIST handbook: exact test for categorical data.</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
+          <t>https://www.itl.nist.gov/div898/handbook/prc/section3/prc33.htm</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
           <t>https://www.fda.gov/regulatory-information/search-fda-guidance-documents</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
@@ -16849,15 +17042,19 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Study unblinding protocols and emergency unblinding.</t>
+          <t>ICH E9 guidance on unblinding protocols.</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E9_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
           <t>https://www.fda.gov/regulatory-information/search-fda-guidance-documents</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -17118,10 +17315,14 @@
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
+          <t>https://www.ich.org/page/ich-guidelines</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
           <t>https://database.ich.org/sites/default/files/E17EWG_Step4_2017_1116.pdf</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
@@ -17185,10 +17386,14 @@
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
+          <t>https://www.ich.org/page/ich-guidelines</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
           <t>https://database.ich.org/sites/default/files/E9-R1_Step4_Guideline_2019_1203.pdf</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
@@ -17286,53 +17491,58 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17345,7 +17555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -17412,7 +17622,11 @@
           <t>https://phuse.s3.eu-central-1.amazonaws.com/Deliverables/Optimizing+the+Use+of+Data+Standards/Best+Practices+for+Documenting+Dataset+Metadata-Define-XML+Versus+Reviewers+Guide.pdf</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr"/>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>https://advance.hub.phuse.global/</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
@@ -17433,7 +17647,11 @@
           <t>https://phuse.s3.eu-central-1.amazonaws.com/Deliverables/Optimizing+the+Use+of+Data+Standards/Define-XML+Version+2.0+Completion+Guidelines.pdf</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr"/>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>https://advance.hub.phuse.global/</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -17454,7 +17672,11 @@
           <t>https://phuse.s3.eu-central-1.amazonaws.com/Deliverables/Optimizing+the+Use+of+Data+Standards/Define-XML+Version+2.0+Completion+Guidelines.pdf</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr"/>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>https://advance.hub.phuse.global/</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -17542,7 +17764,11 @@
           <t>https://www.lexjansen.com/phuse/2018/sa/SA04.pdf</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>https://www.lexjansen.com/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -17584,7 +17810,11 @@
           <t>https://www.lexjansen.com/pharmasug/2017/DS/PharmaSUG-2017-DS14.pdf</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>https://www.lexjansen.com/</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -17605,7 +17835,11 @@
           <t>https://www.lexjansen.com/phuse/2024/si/PAP_SI06.pdf</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.lexjansen.com/</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -18354,10 +18588,14 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/movefile/n1xbwdre0giahfn11c99yjkpi2yb.htm</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
@@ -18568,7 +18806,11 @@
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr"/>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>https://estri.ich.org/</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
@@ -18586,10 +18828,14 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/M4_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
@@ -18628,10 +18874,14 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/M4E_R2__Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
@@ -18673,7 +18923,11 @@
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr"/>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>https://estri.ich.org/eCTD/</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
@@ -18712,10 +18966,14 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
+          <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
           <t>https://estri.ich.org/eCTD/</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
@@ -18723,12 +18981,12 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>eCTD v3.2.2 Specification</t>
+          <t>eCTD v4.0 Specification</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Current widely-used eCTD version.</t>
+          <t>XML-based eCTD replacing folder-based v3.2.2.</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -18744,7 +19002,7 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>eCTD v4.0 Specification</t>
+          <t>eCTD v4.0 Standard</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -18757,95 +19015,90 @@
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>eCTD v4.0 Standard</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>XML-based eCTD replacing folder-based v3.2.2.</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
+      <c r="E72" s="9" t="inlineStr">
         <is>
           <t>https://estri.ich.org/eCTD/</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E73"/>
+  <autoFilter ref="A1:E72"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18858,7 +19111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -19387,52 +19640,52 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>ICH E2A</t>
+          <t>Risk Management Plan (RMP) Guidance</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Clinical Safety Data Management: Expedited Reporting.</t>
+          <t>EMA guidance on Risk Management Plans for marketing authorization.</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>https://database.ich.org/sites/default/files/E2A_Guideline.pdf</t>
+          <t>https://www.ema.europa.eu/en/good-pharmacovigilance-practices</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>PV SOFTWARE</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Risk Management Plan (RMP) Guidance</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>EMA guidance on Risk Management Plans for marketing authorization.</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>https://www.ema.europa.eu/en/good-pharmacovigilance-practices</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="35" t="inlineStr">
-        <is>
-          <t>PV SOFTWARE</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Oracle Argus Safety</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Leading pharmacovigilance case management.</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/health-sciences/argus/</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
@@ -19440,52 +19693,52 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Oracle Argus Safety</t>
+          <t>Veeva Vault Safety</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Leading pharmacovigilance case management.</t>
+          <t>Cloud-native safety case management.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>https://www.oracle.com/health-sciences/argus/</t>
+          <t>https://www.veeva.com/products/vault-safety/</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>SAFETY ANALYSIS TOOLS</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Veeva Vault Safety</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Cloud-native safety case management.</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>https://www.veeva.com/products/vault-safety/</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="35" t="inlineStr">
-        <is>
-          <t>SAFETY ANALYSIS TOOLS</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>CIOMS VI — Management of Safety Information</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>CIOMS working group VI report.</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>https://cioms.ch/publications/</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
@@ -19493,17 +19746,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>CIOMS VI — Management of Safety Information</t>
+          <t>PhUSE Standard Safety Displays</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>CIOMS working group VI report.</t>
+          <t>Standard safety tables and figures from PhUSE WG.</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>https://cioms.ch/publications/</t>
+          <t>https://advance.hub.phuse.global/</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr"/>
@@ -19514,52 +19767,52 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>PhUSE Standard Safety Displays</t>
+          <t>gsm — Good Statistical Monitoring (R)</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Standard safety tables and figures from PhUSE WG.</t>
+          <t>Risk-based statistical site monitoring.</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>https://advance.hub.phuse.global/</t>
+          <t>https://github.com/Gilead-BioStats/gsm</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="35" t="inlineStr">
+        <is>
+          <t>SAFETY REPORTING STANDARDS</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>gsm — Good Statistical Monitoring (R)</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Risk-based statistical site monitoring.</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/Gilead-BioStats/gsm</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="n"/>
-      <c r="B37" s="35" t="inlineStr">
-        <is>
-          <t>SAFETY REPORTING STANDARDS</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>CIOMS Forms (I-V)</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Council for International Organizations of Medical Sciences.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>https://cioms.ch/</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
@@ -19567,17 +19820,17 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>CIOMS Forms (I-V)</t>
+          <t>ICH E2A Expedited Reporting</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Council for International Organizations of Medical Sciences.</t>
+          <t>Definitions and standards for expedited AE reporting.</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>https://cioms.ch/</t>
+          <t>https://database.ich.org/sites/default/files/E2A_Guideline.pdf</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr"/>
@@ -19588,17 +19841,17 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ICH E2A Expedited Reporting</t>
+          <t>ICH E2B(R3) ICSR</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Definitions and standards for expedited AE reporting.</t>
+          <t>Individual Case Safety Report data elements.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>https://database.ich.org/sites/default/files/E2A_Guideline.pdf</t>
+          <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr"/>
@@ -19609,12 +19862,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ICH E2B(R3) ICSR</t>
+          <t>ICH E2C(R2) PBRER</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Individual Case Safety Report data elements.</t>
+          <t>Periodic Benefit-Risk Evaluation Report.</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -19630,12 +19883,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ICH E2C(R2) PBRER</t>
+          <t>ICH E2D Post-Approval Safety</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Periodic Benefit-Risk Evaluation Report.</t>
+          <t>Post-approval safety data management.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -19651,12 +19904,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ICH E2D Post-Approval Safety</t>
+          <t>ICH E2E Pharmacovigilance Planning</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Post-approval safety data management.</t>
+          <t>PV planning for drug development.</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
@@ -19672,12 +19925,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ICH E2E Pharmacovigilance Planning</t>
+          <t>ICH E2F DSUR</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>PV planning for drug development.</t>
+          <t>Development Safety Update Report.</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -19688,36 +19941,36 @@
       <c r="E43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="n">
+      <c r="A44" s="6" t="n"/>
+      <c r="B44" s="35" t="inlineStr">
+        <is>
+          <t>SIGNAL DETECTION</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>ICH E2F DSUR</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>Development Safety Update Report.</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>https://www.ich.org/page/efficacy-guidelines</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="n"/>
-      <c r="B45" s="35" t="inlineStr">
-        <is>
-          <t>SIGNAL DETECTION</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Canada Vigilance Online</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Canadian adverse reaction database.</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>https://www.canada.ca/en/health-canada/services/drugs-health-products/medeffect-canada/canada-vigilance-program.html</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
@@ -19725,17 +19978,17 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Canada Vigilance Online</t>
+          <t>EMA DARWIN EU</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Canadian adverse reaction database.</t>
+          <t>EU real-world data network for regulatory.</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>https://www.canada.ca/en/health-canada/services/drugs-health-products/medeffect-canada/canada-vigilance-program.html</t>
+          <t>https://www.darwin-eu.org/</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr"/>
@@ -19746,17 +19999,17 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>EMA DARWIN EU</t>
+          <t>EMA Signal Management Guideline</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>EU real-world data network for regulatory.</t>
+          <t>GVP Module IX — Signal management.</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>https://www.darwin-eu.org/</t>
+          <t>https://www.ema.europa.eu/en/human-regulatory-overview/post-authorisation/pharmacovigilance/good-pharmacovigilance-practices</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr"/>
@@ -19767,17 +20020,17 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>EMA Signal Management Guideline</t>
+          <t>FDA Sentinel System</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>GVP Module IX — Signal management.</t>
+          <t>Active surveillance of medical products.</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>https://www.ema.europa.eu/en/human-regulatory-overview/post-authorisation/pharmacovigilance/good-pharmacovigilance-practices</t>
+          <t>https://www.sentinelinitiative.org/</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr"/>
@@ -19788,17 +20041,17 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>FDA Sentinel System</t>
+          <t>PRR (Proportional Reporting Ratio)</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Active surveillance of medical products.</t>
+          <t>Signal detection statistical method.</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>https://www.sentinelinitiative.org/</t>
+          <t>https://www.who-umc.org/</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr"/>
@@ -19809,17 +20062,17 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>PRR (Proportional Reporting Ratio)</t>
+          <t>PhUSE FMQ Repository</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Signal detection statistical method.</t>
+          <t>FDA Medical Queries (standardized AE groupings).</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>https://www.who-umc.org/</t>
+          <t>https://advance.hub.phuse.global</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr"/>
@@ -19830,17 +20083,17 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>PhUSE FMQ Repository</t>
+          <t>VigiAccess</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>FDA Medical Queries (standardized AE groupings).</t>
+          <t>Public interface to VigiBase.</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>https://advance.hub.phuse.global</t>
+          <t>https://www.vigiaccess.org/</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr"/>
@@ -19851,17 +20104,17 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>VigiAccess</t>
+          <t>WHO VigiBase</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Public interface to VigiBase.</t>
+          <t>WHO global ICSR database. 40M+ reports.</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>https://www.vigiaccess.org/</t>
+          <t>https://www.who-umc.org/vigibase/vigibase/</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr"/>
@@ -19872,44 +20125,23 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>WHO VigiBase</t>
+          <t>openFDA API</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>WHO global ICSR database. 40M+ reports.</t>
+          <t>FDA public data API (FAERS, labels, recalls).</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>https://www.who-umc.org/vigibase/vigibase/</t>
+          <t>https://open.fda.gov/</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr"/>
     </row>
-    <row r="54">
-      <c r="A54" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>openFDA API</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>FDA public data API (FAERS, labels, recalls).</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>https://open.fda.gov/</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E54"/>
+  <autoFilter ref="A1:E53"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
@@ -19932,19 +20164,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId37"/>
@@ -19953,7 +20185,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23013,10 +23244,14 @@
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p069f7bj3zj58bn1v4gkqzzb5fex.htm</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
@@ -23112,7 +23347,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24290,12 +24526,12 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADAE</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/ADaM/ADAE</t>
         </is>
       </c>
     </row>
@@ -24315,10 +24551,14 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADCM</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -24336,10 +24576,14 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADEG</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -24357,10 +24601,14 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADEX</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
@@ -24378,10 +24626,14 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADLB</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
@@ -24399,10 +24651,14 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADPC</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -24420,10 +24676,14 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADPP</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
@@ -24441,10 +24701,14 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADQS</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
@@ -24462,10 +24726,14 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADRS</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
@@ -24483,12 +24751,12 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADSL</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/ADaM/ADSL</t>
         </is>
       </c>
     </row>
@@ -24508,10 +24776,14 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADTR</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
@@ -24529,12 +24801,12 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADTTE</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/ADaM/ADTTE</t>
         </is>
       </c>
     </row>
@@ -24554,10 +24826,14 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/ADVS</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
@@ -24575,12 +24851,12 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/BDS</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/ADaM/BDS</t>
         </is>
       </c>
     </row>
@@ -24600,12 +24876,12 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/ADaM/OCCDS</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/adam</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/ADaM/OCCDS</t>
         </is>
       </c>
     </row>
@@ -25881,7 +26157,11 @@
           <t>https://phuse.s3.eu-central-1.amazonaws.com/Deliverables/Optimizing+the+Use+of+Data+Standards/Define-XML+Version+2.0+Completion+Guidelines.pdf</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr"/>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>https://advance.hub.phuse.global/</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
@@ -28227,12 +28507,12 @@
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/AE</t>
+        </is>
+      </c>
+      <c r="E209" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E209" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/AE</t>
         </is>
       </c>
     </row>
@@ -28252,12 +28532,12 @@
       </c>
       <c r="D210" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/CE</t>
+        </is>
+      </c>
+      <c r="E210" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E210" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/CE</t>
         </is>
       </c>
     </row>
@@ -28277,12 +28557,12 @@
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/DS</t>
+        </is>
+      </c>
+      <c r="E211" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E211" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/DS</t>
         </is>
       </c>
     </row>
@@ -28302,12 +28582,12 @@
       </c>
       <c r="D212" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/DV</t>
+        </is>
+      </c>
+      <c r="E212" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E212" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/DV</t>
         </is>
       </c>
     </row>
@@ -28327,12 +28607,12 @@
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/HO</t>
+        </is>
+      </c>
+      <c r="E213" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E213" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/HO</t>
         </is>
       </c>
     </row>
@@ -28352,12 +28632,12 @@
       </c>
       <c r="D214" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/MH</t>
+        </is>
+      </c>
+      <c r="E214" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E214" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/MH</t>
         </is>
       </c>
     </row>
@@ -28388,12 +28668,12 @@
       </c>
       <c r="D216" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/AG</t>
+        </is>
+      </c>
+      <c r="E216" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E216" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/AG</t>
         </is>
       </c>
     </row>
@@ -28413,12 +28693,12 @@
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/BE</t>
+        </is>
+      </c>
+      <c r="E217" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E217" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/BE</t>
         </is>
       </c>
     </row>
@@ -28463,12 +28743,12 @@
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/DA</t>
+        </is>
+      </c>
+      <c r="E219" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E219" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/DA</t>
         </is>
       </c>
     </row>
@@ -28488,12 +28768,12 @@
       </c>
       <c r="D220" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/DD</t>
+        </is>
+      </c>
+      <c r="E220" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E220" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/DD</t>
         </is>
       </c>
     </row>
@@ -28513,12 +28793,12 @@
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/DI</t>
+        </is>
+      </c>
+      <c r="E221" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E221" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/DI</t>
         </is>
       </c>
     </row>
@@ -28538,12 +28818,12 @@
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/EG</t>
+        </is>
+      </c>
+      <c r="E222" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E222" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/EG</t>
         </is>
       </c>
     </row>
@@ -28563,12 +28843,12 @@
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/FT</t>
+        </is>
+      </c>
+      <c r="E223" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E223" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/FT</t>
         </is>
       </c>
     </row>
@@ -28613,12 +28893,12 @@
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/IE</t>
+        </is>
+      </c>
+      <c r="E225" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E225" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/IE</t>
         </is>
       </c>
     </row>
@@ -28638,12 +28918,12 @@
       </c>
       <c r="D226" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/IS</t>
+        </is>
+      </c>
+      <c r="E226" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E226" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/IS</t>
         </is>
       </c>
     </row>
@@ -28663,12 +28943,12 @@
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/LB</t>
+        </is>
+      </c>
+      <c r="E227" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E227" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/LB</t>
         </is>
       </c>
     </row>
@@ -28688,12 +28968,12 @@
       </c>
       <c r="D228" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/MB</t>
+        </is>
+      </c>
+      <c r="E228" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E228" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/MB</t>
         </is>
       </c>
     </row>
@@ -28713,12 +28993,12 @@
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/MI</t>
+        </is>
+      </c>
+      <c r="E229" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E229" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/MI</t>
         </is>
       </c>
     </row>
@@ -28738,12 +29018,12 @@
       </c>
       <c r="D230" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/MO</t>
+        </is>
+      </c>
+      <c r="E230" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E230" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/MO</t>
         </is>
       </c>
     </row>
@@ -28763,12 +29043,12 @@
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/MS</t>
+        </is>
+      </c>
+      <c r="E231" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E231" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/MS</t>
         </is>
       </c>
     </row>
@@ -28788,12 +29068,12 @@
       </c>
       <c r="D232" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/NV</t>
+        </is>
+      </c>
+      <c r="E232" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E232" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/NV</t>
         </is>
       </c>
     </row>
@@ -28813,12 +29093,12 @@
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/OE</t>
+        </is>
+      </c>
+      <c r="E233" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E233" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/OE</t>
         </is>
       </c>
     </row>
@@ -28838,12 +29118,12 @@
       </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/PC</t>
+        </is>
+      </c>
+      <c r="E234" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E234" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/PC</t>
         </is>
       </c>
     </row>
@@ -28863,12 +29143,12 @@
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/PE</t>
+        </is>
+      </c>
+      <c r="E235" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E235" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/PE</t>
         </is>
       </c>
     </row>
@@ -28888,12 +29168,12 @@
       </c>
       <c r="D236" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/PP</t>
+        </is>
+      </c>
+      <c r="E236" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E236" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/PP</t>
         </is>
       </c>
     </row>
@@ -28913,12 +29193,12 @@
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/QS</t>
+        </is>
+      </c>
+      <c r="E237" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E237" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/QS</t>
         </is>
       </c>
     </row>
@@ -28938,12 +29218,12 @@
       </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/RE</t>
+        </is>
+      </c>
+      <c r="E238" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E238" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/RE</t>
         </is>
       </c>
     </row>
@@ -28963,12 +29243,12 @@
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/RP</t>
+        </is>
+      </c>
+      <c r="E239" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E239" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/RP</t>
         </is>
       </c>
     </row>
@@ -28988,12 +29268,12 @@
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/RS</t>
+        </is>
+      </c>
+      <c r="E240" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E240" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/RS</t>
         </is>
       </c>
     </row>
@@ -29013,12 +29293,12 @@
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/SC</t>
+        </is>
+      </c>
+      <c r="E241" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E241" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/SC</t>
         </is>
       </c>
     </row>
@@ -29038,12 +29318,12 @@
       </c>
       <c r="D242" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/SS</t>
+        </is>
+      </c>
+      <c r="E242" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E242" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/SS</t>
         </is>
       </c>
     </row>
@@ -29063,12 +29343,12 @@
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/TR</t>
+        </is>
+      </c>
+      <c r="E243" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E243" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/TR</t>
         </is>
       </c>
     </row>
@@ -29088,12 +29368,12 @@
       </c>
       <c r="D244" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/TU</t>
+        </is>
+      </c>
+      <c r="E244" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E244" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/TU</t>
         </is>
       </c>
     </row>
@@ -29113,12 +29393,12 @@
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/VS</t>
+        </is>
+      </c>
+      <c r="E245" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E245" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/VS</t>
         </is>
       </c>
     </row>
@@ -29149,12 +29429,12 @@
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/FA</t>
+        </is>
+      </c>
+      <c r="E247" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E247" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/FA</t>
         </is>
       </c>
     </row>
@@ -29174,12 +29454,12 @@
       </c>
       <c r="D248" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/SR</t>
+        </is>
+      </c>
+      <c r="E248" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E248" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/SR</t>
         </is>
       </c>
     </row>
@@ -29210,12 +29490,12 @@
       </c>
       <c r="D250" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/CM</t>
+        </is>
+      </c>
+      <c r="E250" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E250" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/CM</t>
         </is>
       </c>
     </row>
@@ -29235,12 +29515,12 @@
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/EC</t>
+        </is>
+      </c>
+      <c r="E251" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E251" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/EC</t>
         </is>
       </c>
     </row>
@@ -29260,12 +29540,12 @@
       </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/EX</t>
+        </is>
+      </c>
+      <c r="E252" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E252" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/EX</t>
         </is>
       </c>
     </row>
@@ -29285,12 +29565,12 @@
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/PR</t>
+        </is>
+      </c>
+      <c r="E253" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E253" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/PR</t>
         </is>
       </c>
     </row>
@@ -29310,12 +29590,12 @@
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/SU</t>
+        </is>
+      </c>
+      <c r="E254" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E254" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/SU</t>
         </is>
       </c>
     </row>
@@ -29346,12 +29626,12 @@
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/RELREC</t>
+        </is>
+      </c>
+      <c r="E256" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E256" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/RELREC</t>
         </is>
       </c>
     </row>
@@ -29371,12 +29651,12 @@
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/DM</t>
+        </is>
+      </c>
+      <c r="E257" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E257" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/DM</t>
         </is>
       </c>
     </row>
@@ -29407,12 +29687,12 @@
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/CO</t>
+        </is>
+      </c>
+      <c r="E259" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E259" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/CO</t>
         </is>
       </c>
     </row>
@@ -29432,12 +29712,12 @@
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/DM</t>
+        </is>
+      </c>
+      <c r="E260" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E260" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/DM</t>
         </is>
       </c>
     </row>
@@ -29457,12 +29737,12 @@
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/SE</t>
+        </is>
+      </c>
+      <c r="E261" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E261" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/SE</t>
         </is>
       </c>
     </row>
@@ -29482,12 +29762,12 @@
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/SV</t>
+        </is>
+      </c>
+      <c r="E262" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E262" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/SV</t>
         </is>
       </c>
     </row>
@@ -29518,12 +29798,12 @@
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/TA</t>
+        </is>
+      </c>
+      <c r="E264" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E264" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/TA</t>
         </is>
       </c>
     </row>
@@ -29543,12 +29823,12 @@
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/TD</t>
+        </is>
+      </c>
+      <c r="E265" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E265" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/TD</t>
         </is>
       </c>
     </row>
@@ -29568,12 +29848,12 @@
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/TE</t>
+        </is>
+      </c>
+      <c r="E266" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E266" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/TE</t>
         </is>
       </c>
     </row>
@@ -29593,12 +29873,12 @@
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/TI</t>
+        </is>
+      </c>
+      <c r="E267" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E267" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/TI</t>
         </is>
       </c>
     </row>
@@ -29618,12 +29898,12 @@
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/TS</t>
+        </is>
+      </c>
+      <c r="E268" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E268" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/TS</t>
         </is>
       </c>
     </row>
@@ -29643,12 +29923,12 @@
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
+          <t>https://wiki.cdisc.org/display/SDTMIG/TV</t>
+        </is>
+      </c>
+      <c r="E269" s="9" t="inlineStr">
+        <is>
           <t>https://www.cdisc.org/standards/foundational/sdtmig</t>
-        </is>
-      </c>
-      <c r="E269" s="9" t="inlineStr">
-        <is>
-          <t>https://wiki.cdisc.org/display/SDTMIG/TV</t>
         </is>
       </c>
     </row>
@@ -30997,379 +31277,390 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId399"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -32061,7 +32352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -32580,17 +32871,17 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>ICH E3</t>
+          <t>ICH M4E(R2) CTD Module 5</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Structure and Content of Clinical Study Reports.</t>
+          <t>Efficacy module format.</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>https://database.ich.org/sites/default/files/E3_Guideline.pdf</t>
+          <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr"/>
@@ -32601,52 +32892,52 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>ICH M4E(R2) CTD Module 5</t>
+          <t>TransCelerate CPT</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Efficacy module format.</t>
+          <t>Common Protocol Template.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
+          <t>https://www.transceleratebiopharmainc.com/initiatives/clinical-content-reuse/</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>PATIENT ENGAGEMENT</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>TransCelerate CPT</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Common Protocol Template.</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>https://www.transceleratebiopharmainc.com/initiatives/clinical-content-reuse/</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="43" t="inlineStr">
-        <is>
-          <t>PATIENT ENGAGEMENT</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>PFDD Guidance Series (FDA)</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Patient-Focused Drug Development guidance 1-4.</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fda.gov/drugs/development-approval-process-drugs/fda-patient-focused-drug-development-guidance-series</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
@@ -32654,84 +32945,84 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>PFDD Guidance Series (FDA)</t>
+          <t>PatientsLikeMe</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Patient-Focused Drug Development guidance 1-4.</t>
+          <t>Patient-reported outcomes community.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/drugs/development-approval-process-drugs/fda-patient-focused-drug-development-guidance-series</t>
+          <t>https://www.patientslikeme.com/</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>PROJECT MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>PatientsLikeMe</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Patient-reported outcomes community.</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>https://www.patientslikeme.com/</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n"/>
-      <c r="B34" s="43" t="inlineStr">
-        <is>
-          <t>PROJECT MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>TransCelerate ICH E6(R3) Tools</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>15 practical tools for GCP R3 implementation.</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>https://www.transceleratebiopharmainc.com/assets/ich-e6-asset-library/</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="6" t="n"/>
+      <c r="B35" s="43" t="inlineStr">
+        <is>
+          <t>QUALITY &amp; RBQM</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>TransCelerate ICH E6(R3) Tools</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>15 practical tools for GCP R3 implementation.</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>https://www.transceleratebiopharmainc.com/assets/ich-e6-asset-library/</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n"/>
-      <c r="B36" s="43" t="inlineStr">
-        <is>
-          <t>QUALITY &amp; RBQM</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>CRO Oversight Guidance</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Sponsor responsibilities for CRO oversight per ICH E6.</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fda.gov/regulatory-information/search-fda-guidance-documents</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
@@ -32739,17 +33030,17 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>CRO Oversight Guidance</t>
+          <t>EMA Risk-Based QMS Guideline</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Sponsor responsibilities for CRO oversight per ICH E6.</t>
+          <t>EU risk-based quality management.</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/regulatory-information/search-fda-guidance-documents</t>
+          <t>https://www.ema.europa.eu/en/human-regulatory-overview/research-development/scientific-guidelines</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr"/>
@@ -32760,17 +33051,17 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>EMA Risk-Based QMS Guideline</t>
+          <t>FDA RBQM Guidance</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>EU risk-based quality management.</t>
+          <t>Risk-based approach to monitoring.</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>https://www.ema.europa.eu/en/human-regulatory-overview/research-development/scientific-guidelines</t>
+          <t>https://www.fda.gov/regulatory-information/search-fda-guidance-documents/risk-based-monitoring</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr"/>
@@ -32781,17 +33072,17 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>FDA RBQM Guidance</t>
+          <t>ICH E6(R3) GCP</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Risk-based approach to monitoring.</t>
+          <t>GCP revision - risk-based quality management.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/regulatory-information/search-fda-guidance-documents/risk-based-monitoring</t>
+          <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr"/>
@@ -32802,17 +33093,17 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ICH E6(R3) GCP</t>
+          <t>Risk-Based Monitoring (RBM) Framework</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>GCP revision - risk-based quality management.</t>
+          <t>ICH E6(R3) risk-based approach to monitoring clinical trials.</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>https://www.ich.org/page/efficacy-guidelines</t>
+          <t>https://www.transceleratebiopharmainc.com/initiatives/risk-based-monitoring/</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr"/>
@@ -32823,52 +33114,52 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Risk-Based Monitoring (RBM) Framework</t>
+          <t>TransCelerate RBQM Framework</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>ICH E6(R3) risk-based approach to monitoring clinical trials.</t>
+          <t>Risk-Based Quality Management toolkit.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>https://www.transceleratebiopharmainc.com/initiatives/risk-based-monitoring/</t>
+          <t>https://www.transceleratebiopharmainc.com/</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n">
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="43" t="inlineStr">
+        <is>
+          <t>RTSM / IRT</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>TransCelerate RBQM Framework</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Risk-Based Quality Management toolkit.</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>https://www.transceleratebiopharmainc.com/</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="43" t="inlineStr">
-        <is>
-          <t>RTSM / IRT</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Medidata Rave RTSM</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Randomization and Trial Supply Management.</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>https://www.medidata.com/en/clinical-trial-products/</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
@@ -32876,84 +33167,84 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Medidata Rave RTSM</t>
+          <t>Oracle Clinical One RTSM</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Randomization and Trial Supply Management.</t>
+          <t>Integrated randomization and supply.</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>https://www.medidata.com/en/clinical-trial-products/</t>
+          <t>https://www.oracle.com/health-sciences/clinical-one/</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="n">
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="43" t="inlineStr">
+        <is>
+          <t>SAFETY DATABASES</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Oracle Clinical One RTSM</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>Integrated randomization and supply.</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>https://www.oracle.com/health-sciences/clinical-one/</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="n"/>
-      <c r="B46" s="43" t="inlineStr">
-        <is>
-          <t>SAFETY DATABASES</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>ArisGlobal LifeSphere</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Multi-tenant PV platform.</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>https://www.arisglobal.com/</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="n">
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="43" t="inlineStr">
+        <is>
+          <t>SITE MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>ArisGlobal LifeSphere</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>Multi-tenant PV platform.</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>https://www.arisglobal.com/</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="n"/>
-      <c r="B48" s="43" t="inlineStr">
-        <is>
-          <t>SITE MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n"/>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Florence eBinders</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Electronic regulatory binders for sites.</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>https://www.florencehc.com/</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
@@ -32961,52 +33252,52 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Florence eBinders</t>
+          <t>Veeva SiteVault</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Electronic regulatory binders for sites.</t>
+          <t>Free site ISF and eConsent.</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>https://www.florencehc.com/</t>
+          <t>https://www.veeva.com/products/sitevault/</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="n">
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="43" t="inlineStr">
+        <is>
+          <t>TEMPLATES</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Veeva SiteVault</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>Free site ISF and eConsent.</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>https://www.veeva.com/products/sitevault/</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="n"/>
-      <c r="B51" s="43" t="inlineStr">
-        <is>
-          <t>TEMPLATES</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Data Transfer Agreement (DTA) Template</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Template for data transfer specifications between sponsor and vendors.</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>https://advance.hub.phuse.global/</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
@@ -33014,12 +33305,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Data Transfer Agreement (DTA) Template</t>
+          <t>SOP Templates for Clinical Programming</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Template for data transfer specifications between sponsor and vendors.</t>
+          <t>Standard Operating Procedure templates for programming teams.</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -33030,36 +33321,36 @@
       <c r="E52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="n">
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="43" t="inlineStr">
+        <is>
+          <t>eCOA / ePRO</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>SOP Templates for Clinical Programming</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>Standard Operating Procedure templates for programming teams.</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>https://advance.hub.phuse.global/</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="n"/>
-      <c r="B54" s="43" t="inlineStr">
-        <is>
-          <t>eCOA / ePRO</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="6" t="n"/>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>ERT (Clario) eCOA</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>eCOA/ePRO for clinical trials.</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>https://clario.com/</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
@@ -33067,17 +33358,17 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>ERT (Clario) eCOA</t>
+          <t>FDA COA Guidance</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>eCOA/ePRO for clinical trials.</t>
+          <t>Clinical Outcome Assessments qualification.</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>https://clario.com/</t>
+          <t>https://www.fda.gov/drugs/development-approval-process-drugs/clinical-outcome-assessment-compendium</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr"/>
@@ -33088,52 +33379,52 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>FDA COA Guidance</t>
+          <t>Medidata Patient Cloud eCOA</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Clinical Outcome Assessments qualification.</t>
+          <t>Electronic Clinical Outcome Assessment.</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/drugs/development-approval-process-drugs/clinical-outcome-assessment-compendium</t>
+          <t>https://www.medidata.com/en/clinical-trial-products/</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="n">
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="43" t="inlineStr">
+        <is>
+          <t>eConsent</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Medidata Patient Cloud eCOA</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>Electronic Clinical Outcome Assessment.</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>https://www.medidata.com/en/clinical-trial-products/</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="n"/>
-      <c r="B58" s="43" t="inlineStr">
-        <is>
-          <t>eConsent</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="n"/>
-      <c r="D58" s="6" t="n"/>
-      <c r="E58" s="6" t="n"/>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Medidata myMedidata eConsent</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Electronic informed consent.</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>https://www.medidata.com/en/clinical-trial-products/patient-engagement/econsent/</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
@@ -33141,52 +33432,52 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Medidata myMedidata eConsent</t>
+          <t>Signant Health eConsent</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Electronic informed consent.</t>
+          <t>Visual eConsent platform.</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>https://www.medidata.com/en/clinical-trial-products/patient-engagement/econsent/</t>
+          <t>https://www.signanthealth.com/</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="n">
+      <c r="A60" s="6" t="n"/>
+      <c r="B60" s="43" t="inlineStr">
+        <is>
+          <t>eTMF SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Signant Health eConsent</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>Visual eConsent platform.</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>https://www.signanthealth.com/</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="n"/>
-      <c r="B61" s="43" t="inlineStr">
-        <is>
-          <t>eTMF SYSTEMS</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="6" t="n"/>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Medidata Rave eTMF</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Integrated eTMF solution.</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>https://www.medidata.com/en/clinical-trial-products/</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
@@ -33194,44 +33485,23 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Medidata Rave eTMF</t>
+          <t>TMF Reference Model v4.0</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Integrated eTMF solution.</t>
+          <t>eTMF taxonomy. 217 artifacts, 9 zones.</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>https://www.medidata.com/en/clinical-trial-products/</t>
+          <t>https://www.tmfrefmodel.com</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr"/>
     </row>
-    <row r="63">
-      <c r="A63" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>TMF Reference Model v4.0</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>eTMF taxonomy. 217 artifacts, 9 zones.</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>https://www.tmfrefmodel.com</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E63"/>
+  <autoFilter ref="A1:E62"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
@@ -33254,30 +33524,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36330,12 +36599,12 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E1_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>https://database.ich.org/sites/default/files/E1_Guideline.pdf</t>
         </is>
       </c>
     </row>
@@ -36355,10 +36624,14 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E10_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -36376,10 +36649,14 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E11_R1__Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -36397,12 +36674,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E12A_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>https://database.ich.org/sites/default/files/E12A_Guideline.pdf</t>
         </is>
       </c>
     </row>
@@ -36450,7 +36727,11 @@
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/E14_IWG_Step4_Guideline_2020_1112.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -36521,7 +36802,11 @@
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/E17EWG_Step4_2017_1116.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -36539,10 +36824,14 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E18_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -36563,7 +36852,11 @@
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/E19_Step4_Guideline_2019_1205.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -36581,12 +36874,12 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E1A_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>https://database.ich.org/sites/default/files/E1A_Guideline.pdf</t>
         </is>
       </c>
     </row>
@@ -36609,7 +36902,11 @@
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/ICH_E20_Concept_Paper_2023_0213.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -36627,12 +36924,12 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E2A_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>https://database.ich.org/sites/default/files/E2A_Guideline.pdf</t>
         </is>
       </c>
     </row>
@@ -36652,10 +36949,14 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E2B_R3_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -36673,10 +36974,14 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E2C_R2_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -36694,10 +36999,14 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E2D_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
@@ -36715,10 +37024,14 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E2E_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
@@ -36736,10 +37049,14 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E2F_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -36757,12 +37074,12 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E3_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>https://database.ich.org/sites/default/files/E3_Guideline.pdf</t>
         </is>
       </c>
     </row>
@@ -36782,10 +37099,14 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E4_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
@@ -36803,10 +37124,14 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E5_R1__Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
@@ -36870,10 +37195,14 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E7_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
@@ -36891,10 +37220,14 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E8_R1_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
@@ -36912,12 +37245,12 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/E9_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/efficacy-guidelines</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>https://database.ich.org/sites/default/files/E9_Guideline.pdf</t>
         </is>
       </c>
     </row>
@@ -37114,10 +37447,14 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/M10_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
@@ -37138,7 +37475,11 @@
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr"/>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/ICH_M11_Guideline_2024_1121.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
@@ -37159,7 +37500,11 @@
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr"/>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/ICH_M12_Guideline_2024_0516.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
@@ -37180,7 +37525,11 @@
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr"/>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/ICH_M13A_Guideline_2024_0219.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
@@ -37201,7 +37550,11 @@
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/ICH_M14_Concept_Paper_2023_1122.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
@@ -37219,10 +37572,14 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/M2_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
@@ -37240,10 +37597,14 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/M3_R2__Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
@@ -37261,10 +37622,14 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/M4_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
@@ -37282,10 +37647,14 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/M4E_R2__Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
@@ -37303,10 +37672,14 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/M5_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
@@ -37324,10 +37697,14 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/M7_R2_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
@@ -37345,10 +37722,14 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/M8_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
@@ -37366,10 +37747,14 @@
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/M9_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/multidisciplinary-guidelines</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -37398,10 +37783,14 @@
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/Q10_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/quality-guidelines</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
@@ -37444,10 +37833,14 @@
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/Q12_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/quality-guidelines</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
@@ -37465,12 +37858,12 @@
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
+          <t>https://www.ich.org/page/quality-guidelines</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
           <t>https://database.ich.org/sites/default/files/ICH_Q13_Guideline_2022_1116.pdf</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>https://www.ich.org/page/quality-guidelines</t>
         </is>
       </c>
     </row>
@@ -37493,7 +37886,11 @@
           <t>https://www.ich.org/page/quality-guidelines</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr"/>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/ICH_Q14_Guideline_2023_1116.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
@@ -37511,10 +37908,14 @@
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/Q1A_R2_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/quality-guidelines</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
@@ -37535,7 +37936,11 @@
           <t>https://www.ich.org/page/quality-guidelines</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr"/>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/ICH_Q2_R2_Guideline_2022_1116.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
@@ -37645,10 +38050,14 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/Q8_R2_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/quality-guidelines</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
@@ -37669,7 +38078,11 @@
           <t>https://www.ich.org/page/quality-guidelines</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/ICH_Q9_R1_Guideline_2023_0126.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>
@@ -37698,10 +38111,14 @@
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/S10_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/safety-guidelines</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
@@ -37722,7 +38139,11 @@
           <t>https://www.ich.org/page/safety-guidelines</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr"/>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/S11_Step4_Guideline_2020_0218.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
@@ -37743,7 +38164,11 @@
           <t>https://www.ich.org/page/safety-guidelines</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr"/>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/ICH_S12_Guideline_2023_0525.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
@@ -37761,10 +38186,14 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/S1A_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/safety-guidelines</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
@@ -37785,7 +38214,11 @@
           <t>https://www.ich.org/page/safety-guidelines</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr"/>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/S1B-R1_Step4_Guideline_2022_0714.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
@@ -37803,10 +38236,14 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/S2_R1_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/safety-guidelines</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
@@ -37902,7 +38339,11 @@
           <t>https://www.ich.org/page/safety-guidelines</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr"/>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>https://database.ich.org/sites/default/files/S5-R3_Step4_Guideline_2020_0218.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
@@ -37920,10 +38361,14 @@
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/S6_R1_Addendum.pdf</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/safety-guidelines</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
@@ -37941,10 +38386,14 @@
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/S7A_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/safety-guidelines</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
@@ -37962,10 +38411,14 @@
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/S8_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/safety-guidelines</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
@@ -37983,10 +38436,14 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
+          <t>https://database.ich.org/sites/default/files/S9_Guideline.pdf</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
           <t>https://www.ich.org/page/safety-guidelines</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E80"/>
@@ -37994,96 +38451,143 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41572,12 +42076,12 @@
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
+          <t>https://www.ich.org/page/efficacy-guidelines</t>
+        </is>
+      </c>
+      <c r="E171" s="9" t="inlineStr">
+        <is>
           <t>https://database.ich.org/sites/default/files/ICH_E6-R3_GuideLine_2023_1130.pdf</t>
-        </is>
-      </c>
-      <c r="E171" s="9" t="inlineStr">
-        <is>
-          <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
     </row>
@@ -41804,15 +42308,19 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>FDA expectations for SAP elements in clinical trial submissions.</t>
+          <t>FDA expectations for SAP elements based on ICH E9.</t>
         </is>
       </c>
       <c r="D182" s="9" t="inlineStr">
         <is>
+          <t>https://www.fda.gov/regulatory-information/search-fda-guidance-documents/e9-statistical-principles-clinical-trials</t>
+        </is>
+      </c>
+      <c r="E182" s="9" t="inlineStr">
+        <is>
           <t>https://www.fda.gov/regulatory-information/search-fda-guidance-documents</t>
         </is>
       </c>
-      <c r="E182" s="8" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="8" t="n">
@@ -41876,12 +42384,12 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
+          <t>https://www.ich.org/page/efficacy-guidelines</t>
+        </is>
+      </c>
+      <c r="E185" s="9" t="inlineStr">
+        <is>
           <t>https://database.ich.org/sites/default/files/E9-R1_Step4_Guideline_2019_1203.pdf</t>
-        </is>
-      </c>
-      <c r="E185" s="9" t="inlineStr">
-        <is>
-          <t>https://www.ich.org/page/efficacy-guidelines</t>
         </is>
       </c>
     </row>
@@ -42216,15 +42724,19 @@
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Guidance on preparing the Integrated Summary of Effectiveness for NDA.</t>
+          <t>Guidance on preparing ISE for NDA.</t>
         </is>
       </c>
       <c r="D202" s="9" t="inlineStr">
         <is>
+          <t>https://www.fda.gov/media/71481/download</t>
+        </is>
+      </c>
+      <c r="E202" s="9" t="inlineStr">
+        <is>
           <t>https://www.fda.gov/regulatory-information/search-fda-guidance-documents</t>
         </is>
       </c>
-      <c r="E202" s="8" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="8" t="n">
@@ -42237,15 +42749,19 @@
       </c>
       <c r="C203" s="8" t="inlineStr">
         <is>
-          <t>Guidance on preparing the Integrated Summary of Safety for NDA.</t>
+          <t>Guidance on preparing ISS for NDA.</t>
         </is>
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
+          <t>https://www.fda.gov/media/71434/download</t>
+        </is>
+      </c>
+      <c r="E203" s="9" t="inlineStr">
+        <is>
           <t>https://www.fda.gov/regulatory-information/search-fda-guidance-documents</t>
         </is>
       </c>
-      <c r="E203" s="8" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="n"/>
@@ -42595,36 +43111,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId211"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47976,10 +48495,14 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p069f7bj3zj58bn1v4gkqzzb5fex.htm</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -48103,10 +48626,14 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/grstatproc/</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr"/>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/grstatproc/p15comn5qdjndmn1mtqfbwqvv13t.htm</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
@@ -48124,10 +48651,14 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/grstatproc/</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr"/>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/grstatproc/p1spe31bfgjq5sn1kh28xa1aucjl.htm</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -48145,10 +48676,14 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/grstatproc/</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr"/>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/grstatproc/p0qhp42k0jrx4sn1kxlcsr0hekq0.htm</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -48166,10 +48701,14 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/grstatproc/</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr"/>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/grstatproc/p0lhveipkk07v9n1g8o6hq1eexjy.htm</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -48240,10 +48779,14 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/lrcon/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/lrcon/p1wj0wt2ebe2a0n1lv4lem9hdc0v.htm</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
@@ -48377,10 +48920,14 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/lrcon/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/lrcon/p14543smfjbhdqn1kqo6tm8pjnp3.htm</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
@@ -48440,10 +48987,14 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p0t0sjstnsfn39n177ksr37mwzmo.htm</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
@@ -48524,10 +49075,14 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/n0k5fr3n3c2o3gn1093dnqyjqxa5.htm</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
@@ -48755,10 +49310,14 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p1v1bpcjqelr2rn1bfvgt0mjk82f.htm</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
@@ -48818,10 +49377,14 @@
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/grstatproc/n0k5fr3n3c2o3gn1093dnqyjqxa5.htm</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
@@ -48839,10 +49402,14 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/grstatproc/p1yj8vcal96r05n12nxz5jtq73c0.htm</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
@@ -48902,10 +49469,14 @@
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/n1n5z9n8rq5bfin1gljxm9o0p6xn.htm</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
@@ -48944,10 +49515,14 @@
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/n0kmt1fpyxjmemn1ofoq4bv8nmr5.htm</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
@@ -49100,10 +49675,14 @@
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/n1kcw7gsc3f2l4n13q4ks02p5ob7.htm</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
@@ -49121,10 +49700,14 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p0yrrzis0igafyn1wkbvq7kj0wso.htm</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
@@ -49142,10 +49725,14 @@
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p0b7mgkshmz4ztn1ex09ccae6jhe.htm</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
@@ -49184,10 +49771,14 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/movefile/n1xbwdre0giahfn11c99yjkpi2yb.htm</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
@@ -49205,10 +49796,14 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p1kxm9a1wfhyzdn1p18e5iygb67x.htm</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
@@ -49226,10 +49821,14 @@
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p1ixzccqr7c4n1n16yt80pqkrdfz.htm</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
@@ -49247,10 +49846,14 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/n1m4g2ys6n9on2n1v6tgoxaqv0y7.htm</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
@@ -49289,10 +49892,14 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/imlug/imlug_langref_sect001.htm</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
@@ -49310,10 +49917,14 @@
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p0fpeqaam8ateren1h7txgwtsg2ys.htm</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
@@ -49331,10 +49942,14 @@
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p1svqfkr35tg38n1pr8cw3g6xkfm.htm</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
@@ -49373,10 +49988,14 @@
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/grstatproc/n0k5fr3n3c2oafn1r1o2w7e3e53w.htm</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
@@ -49394,10 +50013,14 @@
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p03m8khz0vl0yxn1o0q9kodrszfl.htm</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
@@ -49415,10 +50038,14 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p0fpeqaam8ateren1h7txgwtsg2ys.htm</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
@@ -49573,10 +50200,14 @@
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
+          <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/titlepage.htm</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
           <t>https://documentation.sas.com/doc/en/pgmsascdc/v_052/proc/p069f7bj3zj58bn1v4gkqzzb5fex.htm</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
@@ -49608,81 +50239,109 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId109"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -59151,10 +59810,14 @@
       </c>
       <c r="D465" s="9" t="inlineStr">
         <is>
+          <t>https://github.com/cdisc-org/dataset-json</t>
+        </is>
+      </c>
+      <c r="E465" s="9" t="inlineStr">
+        <is>
           <t>https://smart-dataset-json-viewer.com/</t>
         </is>
       </c>
-      <c r="E465" s="8" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="8" t="n">
@@ -59666,9 +60329,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D463" r:id="rId442"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D464" r:id="rId443"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D465" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D466" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D467" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D468" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E465" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D466" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D467" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D468" r:id="rId448"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
